--- a/examples/excel/charts/charts-bar.xlsx
+++ b/examples/excel/charts/charts-bar.xlsx
@@ -3,13 +3,13 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Bar Fundamentals" sheetId="2" r:id="R3c7357a1075343dc"/>
-    <x:sheet name="2-Bar Variants" sheetId="3" r:id="Rf501798049964b9f"/>
-    <x:sheet name="3-Bar Styling" sheetId="4" r:id="R4b7d0b0dcee442f7"/>
-    <x:sheet name="4-Axis &amp; Labels" sheetId="5" r:id="Rdfda3a548210427a"/>
-    <x:sheet name="5-Legend &amp; Layout" sheetId="6" r:id="R620f4ebabce34d3a"/>
-    <x:sheet name="6-Advanced" sheetId="7" r:id="R9b9d9b76c660453d"/>
-    <x:sheet name="7-Axis Controls" sheetId="8" r:id="R2cb49e30fbb7448b"/>
+    <x:sheet name="1-Bar Fundamentals" sheetId="2" r:id="Rce569fa8861a493e"/>
+    <x:sheet name="2-Bar Variants" sheetId="3" r:id="Rae249a1b265c4203"/>
+    <x:sheet name="3-Bar Styling" sheetId="4" r:id="R1fc122265dab48e8"/>
+    <x:sheet name="4-Axis &amp; Labels" sheetId="5" r:id="R7f955449838947be"/>
+    <x:sheet name="5-Legend &amp; Layout" sheetId="6" r:id="Rf7afc97e61484052"/>
+    <x:sheet name="6-Advanced" sheetId="7" r:id="Rbb81869846c64ca7"/>
+    <x:sheet name="7-Axis Controls" sheetId="8" r:id="Rd06bcac8ae6a4b0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -578,12 +578,12 @@
               </a:pPr>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
-          <c:dLblPos val="outEnd"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
@@ -1181,8 +1181,8 @@
       <c:valAx>
         <c:axId val="2"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="maxMin"/>
-          <c:logBase val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1273,7 +1273,7 @@
                 <c:v>EBITDA</c:v>
               </c:pt>
               <c:pt idx="4">
-                <c:v>Net</c:v>
+                <c:v>Net Income</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -1314,12 +1314,12 @@
               </a:pPr>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
-          <c:dLblPos val="outEnd"/>
           <c:separator>: </c:separator>
         </c:dLbls>
         <c:gapWidth val="150"/>
@@ -1446,9 +1446,21 @@
           </c:dLbls>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
+              <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>Team</c:v>
+                <c:v>Team A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Team B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Team C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Team D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Team E</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -2648,12 +2660,12 @@
           </c:val>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
-          <c:dLblPos val="outEnd"/>
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:axId val="1"/>
@@ -3228,9 +3240,30 @@
           </c:dPt>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
+              <c:ptCount val="8"/>
               <c:pt idx="0">
-                <c:v>Div</c:v>
+                <c:v>Div A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Div B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Div C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Div D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Div E</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>Div F</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>Div G</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>Div H</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -3279,12 +3312,12 @@
               </a:pPr>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
-          <c:dLblPos val="outEnd"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
@@ -4479,7 +4512,6 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:serLines/>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:barChart>
@@ -4559,10 +4591,11 @@
             <c:v>Sales</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -4616,10 +4649,11 @@
             <c:v>Costs</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -6010,9 +6044,21 @@
           </c:spPr>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
+              <c:ptCount val="5"/>
               <c:pt idx="0">
-                <c:v>Dept</c:v>
+                <c:v>Dept A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Dept B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Dept C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Dept D</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>Dept E</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -6111,7 +6157,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf47618ed2df445a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd1f156d98eef4ae9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6141,7 +6187,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R586eb1d9f5fa4464"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6924b33f251341c6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6171,7 +6217,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8c12c1ae9b34acb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb959e3f5a46e4d4c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6201,7 +6247,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R535d8cd2319441ce"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7c584203df2c4bed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6236,7 +6282,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Recad7fc115864fb6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3b8369129edb4810"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6266,7 +6312,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rafaf7e6c78f34133"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbcfd4894dce54d34"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6296,7 +6342,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf5db51d1e3af45b9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R32100d0d7a3e4e2c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6326,7 +6372,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4fa80bbee41343dc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R461dd2a4541a45e8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6361,7 +6407,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R51f09d79b4014feb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rec6fa651500b490e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6391,7 +6437,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R21bbf5d7dd9a4c84"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8eb8a56288284b4a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6421,7 +6467,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2bae37cd25e84a9e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re08ce9a9750c43bf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6451,7 +6497,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra93ce9a331034454"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2172e93d32004957"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6486,7 +6532,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfacbcb10dc0a4d0e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re990118500384403"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6516,7 +6562,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0ad51e3ac424629"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb16fade9c0d428e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6546,7 +6592,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R895cd07eeb5f48e9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc31ff2a64f5c4484"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6576,7 +6622,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb833de32f7e24feb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R646e191b449648a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6611,7 +6657,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26e21e5c99f34ad3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R90db6d1972e74147"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6641,7 +6687,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb25cdf9bf29b4867"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc41e5c63f8ef49aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6671,7 +6717,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a013b58416f474c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R98b7392394454607"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6701,7 +6747,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R962e9f65e0604c27"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4db9ef6a0a5d4b67"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6736,7 +6782,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e0ab2fb0fd84cc6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R26086769d8ee4af7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6766,7 +6812,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb667e22d2424fd9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra03687f573614e50"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6796,7 +6842,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b1347a427c149b4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0efbd7bca2a44d64"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6826,7 +6872,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R08336836eff747fa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3227ae28aa524fb0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6861,7 +6907,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73423736b4a74baf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0a6cf96915484828"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6891,37 +6937,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2529166c2624f3f"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Stacked — axisposition + serlines"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Reb612de8334640db"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R97707451c2894e25"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6942,7 +6958,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Line — markercolor"/>
+        <xdr:cNvPr id="4" name="Line — markercolor"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6951,13 +6967,122 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9ce6517dcd14f2f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf2395b91572a4a6b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7123,48 +7248,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a125bca8a940cf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54ab2db2b62e49d8"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3180c5387664b86"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b1c90200fde4e1a"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R538bf1606923445a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4eaf354d332c47c2"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7493671fbe44f3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a9d42159c264a90"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf32501666ff43b1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b869d8e198342aa"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafb1906616fc4ef8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7c30b3feaf64cda"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0776dacdc443ed"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f75ca89e9df4f90"/>
 </x:worksheet>
 </file>